--- a/outputs/daily/hr_rankings_2026-09-10.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-10.xlsx
@@ -1596,7 +1596,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>61.6</v>
+        <v>61.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>40.2</v>
       </c>
       <c r="R5" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -1653,7 +1653,7 @@
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>56.2</v>
+        <v>60.7</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>660670</t>
+          <t>621566</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ronald Acuña Jr.</t>
+          <t>Matt Olson</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2708,12 +2708,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>59.6</v>
+        <v>59</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2746,26 +2746,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>59.2</v>
+        <v>65.8</v>
       </c>
       <c r="Q9" t="n">
         <v>35.2</v>
       </c>
       <c r="R9" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>100</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2817,97 +2817,97 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.53</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>48.09</t>
+          <t>51.62</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>92.81</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>103.2902</t>
+          <t>103.7965</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.5018</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2398</t>
+          <t>0.2552</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3739</t>
+          <t>0.3551</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>76.05</t>
+          <t>74.53</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>62.81</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1993</t>
+          <t>0.2428</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -2963,47 +2963,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>621566</t>
+          <t>700250</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Matt Olson</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-10T16:15:00Z</t>
+          <t>2026-09-10T23:05:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3026,58 +3026,62 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>65.8</v>
+        <v>63.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>35.2</v>
+        <v>42.2</v>
       </c>
       <c r="R10" t="n">
-        <v>53.9</v>
+        <v>38.2</v>
       </c>
       <c r="S10" t="n">
-        <v>96.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>50.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3097,27 +3101,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/25, 0 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 14.5 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3127,112 +3131,104 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>51.62</t>
+          <t>50.64</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>92.81</t>
+          <t>92.39</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>103.7965</t>
+          <t>102.488</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.5018</t>
+          <t>0.5208</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.2552</t>
+          <t>0.2513</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3551</t>
+          <t>0.3791</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>74.53</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.2428</t>
+          <t>0.2566</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>88.04</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.4198</t>
+          <t>0.4323</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>28.61</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>29.02</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -3243,12 +3239,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>700250</t>
+          <t>682987</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>Spencer Jones</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3273,7 +3269,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3292,7 +3288,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>59</v>
+        <v>58.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3306,11 +3302,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>63.6</v>
+        <v>66.5</v>
       </c>
       <c r="Q11" t="n">
         <v>42.2</v>
@@ -3319,13 +3315,13 @@
         <v>38.2</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>50.3</v>
+        <v>46</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3339,7 +3335,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3364,7 +3360,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3381,12 +3377,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3396,7 +3392,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 7/23, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -3406,72 +3402,72 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>50.64</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>92.39</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>102.488</t>
+          <t>104.2558</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.5208</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2513</t>
+          <t>0.202</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3791</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2566</t>
+          <t>0.201</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3519,47 +3515,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>682987</t>
+          <t>660670</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spencer Jones</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-10T23:05:00Z</t>
+          <t>2026-09-10T16:15:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3568,7 +3564,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>58.8</v>
+        <v>58.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3582,65 +3578,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>66.5</v>
+        <v>59.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>42.2</v>
+        <v>35.2</v>
       </c>
       <c r="R12" t="n">
-        <v>38.2</v>
+        <v>52.9</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>46</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3657,134 +3649,142 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 14.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>13.53</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>48.09</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>104.2558</t>
+          <t>103.2902</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>0.2398</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.3739</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>62.81</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>35.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>0.1993</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>88.04</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.4323</t>
+          <t>0.4198</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>29.02</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>28.61</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3844,7 +3844,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>35.2</v>
       </c>
       <c r="R13" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S13" t="n">
         <v>93.2</v>
@@ -3877,7 +3877,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>36.5</v>
+        <v>40.7</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/29, 1 HR</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4351,52 +4351,52 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>703155</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lazaro Montes</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-10T20:10:00Z</t>
+          <t>2026-09-10T16:15:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -4414,65 +4414,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>65.2</v>
+        <v>46.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>48</v>
+        <v>40.2</v>
       </c>
       <c r="R15" t="n">
-        <v>25.4</v>
+        <v>52.9</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U15" t="n">
-        <v>58.1</v>
+        <v>28.2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4489,134 +4485,142 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/13, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.91</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.6883</t>
+          <t>102.7587</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>0.4145</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.1695</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.323</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>57.86</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>0.1498</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3882</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1581</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>29.25</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>23.92</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -4627,27 +4631,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>671277</t>
+          <t>703155</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luis Garcia</t>
+          <t>Lazaro Montes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-10T23:05:00Z</t>
+          <t>2026-09-10T20:10:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4657,17 +4661,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4676,7 +4680,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>55</v>
+        <v>55.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4690,26 +4694,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>50.5</v>
+        <v>65.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>42.2</v>
+        <v>48</v>
       </c>
       <c r="R16" t="n">
-        <v>38.2</v>
+        <v>25.4</v>
       </c>
       <c r="S16" t="n">
-        <v>90.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>52.5</v>
+        <v>58.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4723,7 +4727,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4748,7 +4752,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4765,134 +4769,134 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 14.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>91.25</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>101.9502</t>
+          <t>99.6883</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4924</t>
+          <t>0.544</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.2086</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3474</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.2314</t>
+          <t>0.369</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.04</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4323</t>
+          <t>0.3882</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.1581</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -4903,56 +4907,56 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>671277</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Luis Garcia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-10T16:15:00Z</t>
+          <t>2026-09-10T23:05:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>54.8</v>
+        <v>55</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4966,58 +4970,62 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>46.2</v>
+        <v>50.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>40.2</v>
+        <v>42.2</v>
       </c>
       <c r="R17" t="n">
-        <v>53.9</v>
+        <v>38.2</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>16.6</v>
+        <v>52.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5037,27 +5045,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 14.5 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5067,112 +5075,104 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>91.91</t>
+          <t>91.25</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>102.7587</t>
+          <t>101.9502</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4145</t>
+          <t>0.4924</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1695</t>
+          <t>0.2086</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>0.3474</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>57.86</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1498</t>
+          <t>0.2314</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>88.04</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.4323</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>23.92</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>29.02</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>54.5</v>
+        <v>54.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>40.2</v>
       </c>
       <c r="R19" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S19" t="n">
         <v>93.2</v>
@@ -5541,7 +5541,7 @@
         <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>55.3</v>
+        <v>59.3</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 11/30 over last 7 games</t>
+          <t>Contact streak: 11/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>35.2</v>
       </c>
       <c r="R22" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S22" t="n">
         <v>94.90000000000001</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>35.2</v>
       </c>
       <c r="R31" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S31" t="n">
         <v>64.3</v>
@@ -8877,7 +8877,7 @@
         <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>39.5</v>
+        <v>31.9</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8929,12 +8929,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 4/19, 1 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -9075,47 +9075,47 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>676551</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brewer Hicklen</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-10T16:15:00Z</t>
+          <t>2026-09-10T17:05:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Zack Wheeler</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>554430</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -9138,26 +9138,26 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>58.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>35.2</v>
+        <v>26.8</v>
       </c>
       <c r="R32" t="n">
-        <v>53.9</v>
+        <v>77.3</v>
       </c>
       <c r="S32" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T32" t="n">
         <v>50</v>
       </c>
       <c r="U32" t="n">
-        <v>19.5</v>
+        <v>39.5</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -9209,27 +9209,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/4, 0 HR</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9239,112 +9239,112 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>89.57</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>104.7423</t>
+          <t>101.4316</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.3951</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1722</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.3635</t>
+          <t>0.3056</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.1935</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>87.05</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.4198</t>
+          <t>0.3242</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1233</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9355,47 +9355,47 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-10T17:05:00Z</t>
+          <t>2026-09-10T23:05:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Zack Wheeler</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>554430</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9418,58 +9418,62 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>40.7</v>
+        <v>29.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>26.8</v>
+        <v>42.2</v>
       </c>
       <c r="R33" t="n">
-        <v>77.3</v>
+        <v>38.2</v>
       </c>
       <c r="S33" t="n">
-        <v>76.2</v>
+        <v>95.5</v>
       </c>
       <c r="T33" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U33" t="n">
-        <v>39.5</v>
+        <v>48.7</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9489,12 +9493,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -9504,12 +9508,12 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Contact streak: 10/31 over last 7 games</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 14.5 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -9519,112 +9523,104 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>89.57</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>101.4316</t>
+          <t>98.431</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.4159</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1722</t>
+          <t>0.1491</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3056</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.1935</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>87.05</t>
+          <t>88.04</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.3242</t>
+          <t>0.4323</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.1233</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>26.58</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>29.02</t>
+        </is>
+      </c>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9635,47 +9631,47 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>676551</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Brewer Hicklen</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-10T23:05:00Z</t>
+          <t>2026-09-10T16:15:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9684,7 +9680,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9698,62 +9694,58 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>29.2</v>
+        <v>58.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>42.2</v>
+        <v>35.2</v>
       </c>
       <c r="R34" t="n">
-        <v>38.2</v>
+        <v>52.9</v>
       </c>
       <c r="S34" t="n">
-        <v>95.5</v>
+        <v>52.4</v>
       </c>
       <c r="T34" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U34" t="n">
-        <v>48.7</v>
+        <v>19.5</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9773,27 +9765,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Contact streak: 10/31 over last 7 games</t>
+          <t>Last 7 games: 1/4, 0 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 14.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -9803,104 +9795,112 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>20.81</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>98.431</t>
+          <t>104.7423</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.4159</t>
+          <t>0.3951</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.1491</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3635</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>69.82</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>88.04</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.4323</t>
+          <t>0.4198</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>29.02</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr"/>
-      <c r="BH34" t="inlineStr"/>
+          <t>28.61</t>
+        </is>
+      </c>
+      <c r="BG34" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -14351,12 +14351,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -14400,7 +14400,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>42.7</v>
+        <v>42.4</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14414,26 +14414,26 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>10.6</v>
+        <v>26.5</v>
       </c>
       <c r="Q51" t="n">
         <v>40.2</v>
       </c>
       <c r="R51" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S51" t="n">
-        <v>94.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T51" t="n">
         <v>78</v>
       </c>
       <c r="U51" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -14485,22 +14485,22 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 1 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
@@ -14515,67 +14515,67 @@
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>87.19</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>97.4717</t>
+          <t>99.0999</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>0.3325</t>
+          <t>0.353</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>0.0928</t>
+          <t>0.1328</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>0.2656</t>
+          <t>0.2697</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>73.37</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>31.67</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>0.1468</t>
+          <t>0.1142</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
@@ -14631,56 +14631,56 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-10T16:15:00Z</t>
+          <t>2026-09-10T20:10:00Z</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>42.5</v>
+        <v>42.2</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -14694,58 +14694,62 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>26.5</v>
+        <v>22.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>40.2</v>
+        <v>48</v>
       </c>
       <c r="R52" t="n">
-        <v>53.9</v>
+        <v>25.4</v>
       </c>
       <c r="S52" t="n">
-        <v>64.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14765,12 +14769,12 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -14780,12 +14784,12 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/29, 0 HR</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -14795,112 +14799,104 @@
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>87.19</t>
+          <t>87.66</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>99.0999</t>
+          <t>98.9221</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>0.3984</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>0.1328</t>
+          <t>0.1282</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>0.2697</t>
+          <t>0.3187</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>73.37</t>
+          <t>70.34</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>31.67</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>0.1142</t>
+          <t>0.1159</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.3882</t>
         </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.1581</t>
         </is>
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>23.92</t>
-        </is>
-      </c>
-      <c r="BG52" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH52" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>29.25</t>
+        </is>
+      </c>
+      <c r="BG52" t="inlineStr"/>
+      <c r="BH52" t="inlineStr"/>
       <c r="BI52" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ52" t="inlineStr"/>
@@ -14911,47 +14907,47 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-10T20:10:00Z</t>
+          <t>2026-09-10T17:05:00Z</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Zack Wheeler</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>554430</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -14960,7 +14956,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -14974,62 +14970,58 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>22.2</v>
+        <v>13.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>48</v>
+        <v>26.8</v>
       </c>
       <c r="R53" t="n">
-        <v>25.4</v>
+        <v>77.3</v>
       </c>
       <c r="S53" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T53" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U53" t="n">
-        <v>18.2</v>
+        <v>32.5</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15049,27 +15041,27 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/29, 0 HR</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -15079,104 +15071,112 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>31.81</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>87.66</t>
+          <t>85.38</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>98.9221</t>
+          <t>97.0317</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>0.3984</t>
+          <t>0.3434</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>0.1282</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>0.3187</t>
+          <t>0.2811</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>70.34</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.72</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.1159</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>87.05</t>
         </is>
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>0.3882</t>
+          <t>0.3242</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>0.1581</t>
+          <t>0.1233</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>29.25</t>
-        </is>
-      </c>
-      <c r="BG53" t="inlineStr"/>
-      <c r="BH53" t="inlineStr"/>
+          <t>26.58</t>
+        </is>
+      </c>
+      <c r="BG53" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr"/>
@@ -15187,47 +15187,47 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-10T17:05:00Z</t>
+          <t>2026-09-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Zack Wheeler</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>554430</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -15250,61 +15250,65 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>13.9</v>
+        <v>40.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>26.8</v>
+        <v>40.2</v>
       </c>
       <c r="R54" t="n">
-        <v>77.3</v>
+        <v>27.6</v>
       </c>
       <c r="S54" t="n">
-        <v>94.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T54" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U54" t="n">
-        <v>32.5</v>
+        <v>43.7</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr"/>
@@ -15321,27 +15325,27 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -15351,112 +15355,104 @@
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>31.81</t>
+          <t>45.51</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>85.38</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>97.0317</t>
+          <t>100.4445</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>0.3434</t>
+          <t>0.4097</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.1818</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>0.2811</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>23.99</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>41.66</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>22.72</t>
+          <t>30.71</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.1688</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>87.05</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>0.3242</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
-          <t>0.1233</t>
+          <t>0.159</t>
         </is>
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>26.58</t>
-        </is>
-      </c>
-      <c r="BG54" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH54" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="BG54" t="inlineStr"/>
+      <c r="BH54" t="inlineStr"/>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr"/>
@@ -15467,27 +15463,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>669224</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-10T23:40:00Z</t>
+          <t>2026-09-10T23:05:00Z</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -15497,17 +15493,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -15516,7 +15512,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -15530,26 +15526,26 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>40.1</v>
+        <v>35.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>40.2</v>
+        <v>42.2</v>
       </c>
       <c r="R55" t="n">
-        <v>27.6</v>
+        <v>38.2</v>
       </c>
       <c r="S55" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T55" t="n">
         <v>80</v>
       </c>
       <c r="U55" t="n">
-        <v>43.7</v>
+        <v>7</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -15563,7 +15559,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -15588,7 +15584,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr"/>
@@ -15615,17 +15611,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 14.5 HR allowed</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -15635,104 +15631,104 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>45.51</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>89.62</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>100.4445</t>
+          <t>100.6455</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>0.4097</t>
+          <t>0.364</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.1818</t>
+          <t>0.1542</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.2909</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>23.99</t>
+          <t>27.53</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>41.66</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>30.71</t>
+          <t>33.21</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.1688</t>
+          <t>0.1505</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.04</t>
         </is>
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.4323</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr"/>
       <c r="BH55" t="inlineStr"/>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr"/>
@@ -15743,56 +15739,56 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>669224</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin Wells</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-10T23:05:00Z</t>
+          <t>2026-09-10T16:15:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15806,62 +15802,58 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>35.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>42.2</v>
+        <v>40.2</v>
       </c>
       <c r="R56" t="n">
-        <v>38.2</v>
+        <v>52.9</v>
       </c>
       <c r="S56" t="n">
-        <v>47.9</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T56" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U56" t="n">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15881,12 +15873,12 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -15896,12 +15888,12 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 14.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -15911,104 +15903,112 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>100.6455</t>
+          <t>97.4717</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>0.3325</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.0928</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.2909</t>
+          <t>0.2656</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>33.21</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.1505</t>
+          <t>0.1468</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>88.04</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.4323</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>29.02</t>
-        </is>
-      </c>
-      <c r="BG56" t="inlineStr"/>
-      <c r="BH56" t="inlineStr"/>
+          <t>23.92</t>
+        </is>
+      </c>
+      <c r="BG56" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH56" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -16368,7 +16368,7 @@
         <v>35.2</v>
       </c>
       <c r="R58" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S58" t="n">
         <v>76.2</v>
@@ -16377,7 +16377,7 @@
         <v>80</v>
       </c>
       <c r="U58" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 0 HR</t>
+          <t>Last 7 games: 2/14, 0 HR</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
@@ -16559,7 +16559,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI58" t="inlineStr">
@@ -17959,47 +17959,47 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-10T20:10:00Z</t>
+          <t>2026-09-10T16:15:00Z</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -18022,62 +18022,58 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>32.1</v>
+        <v>10.2</v>
       </c>
       <c r="Q64" t="n">
-        <v>49.4</v>
+        <v>35.2</v>
       </c>
       <c r="R64" t="n">
-        <v>25.4</v>
+        <v>52.9</v>
       </c>
       <c r="S64" t="n">
-        <v>40.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T64" t="n">
         <v>50</v>
       </c>
       <c r="U64" t="n">
-        <v>37.8</v>
+        <v>39.5</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18097,12 +18093,12 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -18112,12 +18108,12 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.8% barrel, 24.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
@@ -18127,104 +18123,112 @@
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>39.89</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>88.05</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>100.487</t>
+          <t>96.2415</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>0.3543</t>
+          <t>0.3632</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.1008</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.2701</t>
+          <t>0.2969</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>74.34</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>31.68</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.1578</t>
+          <t>0.1182</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.4198</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>0.1624</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>28.82</t>
-        </is>
-      </c>
-      <c r="BG64" t="inlineStr"/>
-      <c r="BH64" t="inlineStr"/>
+          <t>28.61</t>
+        </is>
+      </c>
+      <c r="BG64" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH64" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -18235,56 +18239,56 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>663611</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nick Madrigal</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-10T16:15:00Z</t>
+          <t>2026-09-10T20:10:00Z</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -18298,61 +18302,65 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>6.3</v>
+        <v>32.1</v>
       </c>
       <c r="Q65" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="R65" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="S65" t="n">
         <v>40.2</v>
       </c>
-      <c r="R65" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="S65" t="n">
-        <v>76.2</v>
-      </c>
       <c r="T65" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U65" t="n">
-        <v>14.6</v>
+        <v>37.8</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr"/>
@@ -18374,22 +18382,22 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 5/20, 1 HR</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.8% barrel, 24.2 HR allowed</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
@@ -18399,112 +18407,104 @@
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>39.89</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>88.05</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>95.8241</t>
+          <t>100.487</t>
         </is>
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.3543</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.2701</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>74.34</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0.1578</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>90.03</t>
         </is>
       </c>
       <c r="BD65" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.1624</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>23.92</t>
-        </is>
-      </c>
-      <c r="BG65" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH65" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>28.82</t>
+        </is>
+      </c>
+      <c r="BG65" t="inlineStr"/>
+      <c r="BH65" t="inlineStr"/>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr"/>
@@ -18515,24 +18515,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>663611</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Nick Madrigal</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>2026-09-10T16:15:00Z</t>
@@ -18540,31 +18540,31 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -18578,26 +18578,26 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>10.2</v>
+        <v>6.3</v>
       </c>
       <c r="Q66" t="n">
-        <v>35.2</v>
+        <v>40.2</v>
       </c>
       <c r="R66" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S66" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T66" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U66" t="n">
-        <v>33.7</v>
+        <v>10.6</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -18632,7 +18632,7 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr"/>
@@ -18649,27 +18649,27 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 1 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
@@ -18679,97 +18679,97 @@
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>96.2415</t>
+          <t>95.8241</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>0.3632</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>0.1008</t>
+          <t>0.054</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr">
         <is>
-          <t>0.2969</t>
+          <t>0.298</t>
         </is>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>0.1182</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD66" t="inlineStr">
         <is>
-          <t>0.4198</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>23.92</t>
         </is>
       </c>
       <c r="BG66" t="inlineStr">
@@ -18779,7 +18779,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI66" t="inlineStr">
@@ -19924,7 +19924,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -19948,7 +19948,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>40.2</v>
       </c>
       <c r="R71" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S71" t="n">
         <v>52.4</v>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI71" t="inlineStr">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -21056,7 +21056,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>40.2</v>
       </c>
       <c r="R75" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S75" t="n">
         <v>44.8</v>
@@ -21089,7 +21089,7 @@
         <v>50</v>
       </c>
       <c r="U75" t="n">
-        <v>12</v>
+        <v>13.6</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
@@ -21271,7 +21271,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI75" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>35.8</v>
+        <v>35.3</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>40.2</v>
       </c>
       <c r="R76" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S76" t="n">
         <v>86.40000000000001</v>
@@ -21369,7 +21369,7 @@
         <v>50</v>
       </c>
       <c r="U76" t="n">
-        <v>27</v>
+        <v>20.9</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -21421,12 +21421,12 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
@@ -21436,7 +21436,7 @@
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/30, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
@@ -21551,7 +21551,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI76" t="inlineStr">
@@ -22976,7 +22976,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -23000,7 +23000,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>35.2</v>
       </c>
       <c r="R82" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S82" t="n">
         <v>44.8</v>
@@ -23033,7 +23033,7 @@
         <v>50</v>
       </c>
       <c r="U82" t="n">
-        <v>12</v>
+        <v>17.3</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -23100,7 +23100,7 @@
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
@@ -23215,7 +23215,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI82" t="inlineStr">
@@ -26906,7 +26906,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -26930,7 +26930,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>61.6</v>
+        <v>61.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>40.2</v>
       </c>
       <c r="R5" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -26963,7 +26963,7 @@
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>56.2</v>
+        <v>60.7</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -27993,12 +27993,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>660670</t>
+          <t>621566</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ronald Acuña Jr.</t>
+          <t>Matt Olson</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -28018,12 +28018,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -28042,7 +28042,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>59.6</v>
+        <v>59</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -28056,26 +28056,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>59.2</v>
+        <v>65.8</v>
       </c>
       <c r="Q9" t="n">
         <v>35.2</v>
       </c>
       <c r="R9" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>100</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -28127,97 +28127,97 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.53</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>48.09</t>
+          <t>51.62</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>92.81</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>103.2902</t>
+          <t>103.7965</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.5018</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2398</t>
+          <t>0.2552</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3739</t>
+          <t>0.3551</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>76.05</t>
+          <t>74.53</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>62.81</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1993</t>
+          <t>0.2428</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -28257,7 +28257,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -28273,47 +28273,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>621566</t>
+          <t>700250</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Matt Olson</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-10T16:15:00Z</t>
+          <t>2026-09-10T23:05:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -28336,58 +28336,62 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>65.8</v>
+        <v>63.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>35.2</v>
+        <v>42.2</v>
       </c>
       <c r="R10" t="n">
-        <v>53.9</v>
+        <v>38.2</v>
       </c>
       <c r="S10" t="n">
-        <v>96.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>50.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -28407,27 +28411,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/25, 0 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 14.5 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -28437,112 +28441,104 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>51.62</t>
+          <t>50.64</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>92.81</t>
+          <t>92.39</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>103.7965</t>
+          <t>102.488</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.5018</t>
+          <t>0.5208</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.2552</t>
+          <t>0.2513</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3551</t>
+          <t>0.3791</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>74.53</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.2428</t>
+          <t>0.2566</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>88.04</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.4198</t>
+          <t>0.4323</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>28.61</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>29.02</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -28553,12 +28549,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>700250</t>
+          <t>682987</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>Spencer Jones</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -28583,7 +28579,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -28602,7 +28598,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>59</v>
+        <v>58.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -28616,11 +28612,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>63.6</v>
+        <v>66.5</v>
       </c>
       <c r="Q11" t="n">
         <v>42.2</v>
@@ -28629,13 +28625,13 @@
         <v>38.2</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>50.3</v>
+        <v>46</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -28649,7 +28645,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -28674,7 +28670,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -28691,12 +28687,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -28706,7 +28702,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 7/23, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -28716,72 +28712,72 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>50.64</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>92.39</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>102.488</t>
+          <t>104.2558</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.5208</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2513</t>
+          <t>0.202</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3791</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2566</t>
+          <t>0.201</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -28829,47 +28825,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>682987</t>
+          <t>660670</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spencer Jones</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-10T23:05:00Z</t>
+          <t>2026-09-10T16:15:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -28878,7 +28874,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>58.8</v>
+        <v>58.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -28892,65 +28888,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>66.5</v>
+        <v>59.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>42.2</v>
+        <v>35.2</v>
       </c>
       <c r="R12" t="n">
-        <v>38.2</v>
+        <v>52.9</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>46</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -28967,134 +28959,142 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 14.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>13.53</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>48.09</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>104.2558</t>
+          <t>103.2902</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>0.2398</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.3739</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>62.81</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>35.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>0.1993</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>88.04</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.4323</t>
+          <t>0.4198</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>29.02</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>28.61</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -29130,7 +29130,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -29154,7 +29154,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>35.2</v>
       </c>
       <c r="R13" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S13" t="n">
         <v>93.2</v>
@@ -29187,7 +29187,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>36.5</v>
+        <v>40.7</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -29254,7 +29254,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/29, 1 HR</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -29369,7 +29369,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -29661,52 +29661,52 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>703155</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lazaro Montes</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-10T20:10:00Z</t>
+          <t>2026-09-10T16:15:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -29724,65 +29724,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>65.2</v>
+        <v>46.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>48</v>
+        <v>40.2</v>
       </c>
       <c r="R15" t="n">
-        <v>25.4</v>
+        <v>52.9</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U15" t="n">
-        <v>58.1</v>
+        <v>28.2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -29799,134 +29795,142 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/13, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.91</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.6883</t>
+          <t>102.7587</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>0.4145</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.1695</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.323</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>57.86</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>0.1498</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3882</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1581</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>29.25</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>23.92</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -29937,27 +29941,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>671277</t>
+          <t>703155</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luis Garcia</t>
+          <t>Lazaro Montes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-10T23:05:00Z</t>
+          <t>2026-09-10T20:10:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -29967,17 +29971,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -29986,7 +29990,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>55</v>
+        <v>55.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -30000,26 +30004,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>50.5</v>
+        <v>65.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>42.2</v>
+        <v>48</v>
       </c>
       <c r="R16" t="n">
-        <v>38.2</v>
+        <v>25.4</v>
       </c>
       <c r="S16" t="n">
-        <v>90.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>52.5</v>
+        <v>58.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -30033,7 +30037,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -30058,7 +30062,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -30075,134 +30079,134 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 14.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>91.25</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>101.9502</t>
+          <t>99.6883</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4924</t>
+          <t>0.544</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.2086</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3474</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.2314</t>
+          <t>0.369</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.04</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4323</t>
+          <t>0.3882</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.1581</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -30213,56 +30217,56 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>671277</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Luis Garcia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-10T16:15:00Z</t>
+          <t>2026-09-10T23:05:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>54.8</v>
+        <v>55</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -30276,58 +30280,62 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>46.2</v>
+        <v>50.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>40.2</v>
+        <v>42.2</v>
       </c>
       <c r="R17" t="n">
-        <v>53.9</v>
+        <v>38.2</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>16.6</v>
+        <v>52.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -30347,27 +30355,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 14.5 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -30377,112 +30385,104 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>91.91</t>
+          <t>91.25</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>102.7587</t>
+          <t>101.9502</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4145</t>
+          <t>0.4924</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1695</t>
+          <t>0.2086</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>0.3474</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>57.86</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1498</t>
+          <t>0.2314</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>88.04</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.4323</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>23.92</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>29.02</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -30794,7 +30794,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -30818,7 +30818,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>54.5</v>
+        <v>54.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>40.2</v>
       </c>
       <c r="R19" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="S19" t="n">
         <v>93.2</v>
@@ -30851,7 +30851,7 @@
         <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>55.3</v>
+        <v>59.3</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -30918,7 +30918,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 11/30 over last 7 games</t>
+          <t>Contact streak: 11/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -31033,7 +31033,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-09-10.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-10.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3844,7 +3844,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>40.7</v>
+        <v>39.2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Last 7 games: 7/27, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -4351,52 +4351,52 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>703155</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Lazaro Montes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-10T16:15:00Z</t>
+          <t>2026-09-10T20:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -4414,61 +4414,65 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>46.2</v>
+        <v>65.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>40.2</v>
+        <v>48</v>
       </c>
       <c r="R15" t="n">
-        <v>52.9</v>
+        <v>25.4</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>59.8</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>28.2</v>
+        <v>58.1</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4485,142 +4489,134 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/13, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>91.91</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>102.7587</t>
+          <t>99.6883</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4145</t>
+          <t>0.544</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1695</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>57.86</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1498</t>
+          <t>0.369</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.3882</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.1581</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>23.92</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
+          <t>29.25</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -4631,56 +4627,56 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>703155</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lazaro Montes</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-10T20:10:00Z</t>
+          <t>2026-09-10T16:15:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>55.3</v>
+        <v>55.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4694,65 +4690,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>65.2</v>
+        <v>46.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>48</v>
+        <v>40.2</v>
       </c>
       <c r="R16" t="n">
-        <v>25.4</v>
+        <v>52.9</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>58.1</v>
+        <v>24.9</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4769,134 +4761,142 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/14, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.91</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.6883</t>
+          <t>102.7587</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>0.4145</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.1695</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.323</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>57.86</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>0.1498</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3882</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1581</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>29.25</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>23.92</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>54.6</v>
+        <v>54.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>59.3</v>
+        <v>57.2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 11/28 over last 7 games</t>
+          <t>Contact streak: 11/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>31.9</v>
+        <v>30.3</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 1 HR</t>
+          <t>Last 7 games: 4/20, 1 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9631,47 +9631,47 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>676551</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brewer Hicklen</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-10T16:15:00Z</t>
+          <t>2026-09-10T17:05:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Zack Wheeler</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>554430</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9694,26 +9694,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>58.2</v>
+        <v>41.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>35.2</v>
+        <v>26.8</v>
       </c>
       <c r="R34" t="n">
-        <v>52.9</v>
+        <v>77.3</v>
       </c>
       <c r="S34" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T34" t="n">
         <v>50</v>
       </c>
       <c r="U34" t="n">
-        <v>19.5</v>
+        <v>63.7</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -9765,27 +9765,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/4, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -9795,112 +9795,112 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>104.7423</t>
+          <t>101.4509</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.3951</t>
+          <t>0.4138</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1746</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.3635</t>
+          <t>0.3159</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>68.53</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>37.14</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.1668</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>87.05</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.4198</t>
+          <t>0.3242</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1233</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9911,24 +9911,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>2026-09-10T17:05:00Z</t>
@@ -9936,22 +9936,22 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Zack Wheeler</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>554430</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9960,7 +9960,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -9974,26 +9974,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>41.6</v>
+        <v>25.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>26.8</v>
+        <v>43.9</v>
       </c>
       <c r="R35" t="n">
         <v>77.3</v>
       </c>
       <c r="S35" t="n">
-        <v>64.3</v>
+        <v>76.2</v>
       </c>
       <c r="T35" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>63.7</v>
+        <v>0</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -10045,127 +10045,127 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 7.2 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>88.72</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>101.4509</t>
+          <t>98.3851</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4138</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.1746</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3159</t>
+          <t>0.3242</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>68.53</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>37.14</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>27.52</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1668</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>36.41</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>87.05</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.3242</t>
+          <t>0.4124</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1233</t>
+          <t>0.1691</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>26.58</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
@@ -10191,47 +10191,47 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Julio Rodriguez</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-10T17:05:00Z</t>
+          <t>2026-09-10T20:10:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10254,58 +10254,62 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>25.2</v>
+        <v>45.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>43.9</v>
+        <v>48</v>
       </c>
       <c r="R36" t="n">
-        <v>77.3</v>
+        <v>25.4</v>
       </c>
       <c r="S36" t="n">
-        <v>76.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T36" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC36" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10325,12 +10329,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10340,127 +10344,119 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Last 7 games: 5/30, 0 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 7.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>88.72</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>98.3851</t>
+          <t>102.7713</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.4531</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.1873</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3242</t>
+          <t>0.337</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>66.92</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>38.28</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>27.52</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1678</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.4124</t>
+          <t>0.3882</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.1691</t>
+          <t>0.1581</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>37.75</t>
-        </is>
-      </c>
-      <c r="BG36" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH36" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>29.25</t>
+        </is>
+      </c>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10471,47 +10467,47 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>676551</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Brewer Hicklen</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-10T20:10:00Z</t>
+          <t>2026-09-10T16:15:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -10520,7 +10516,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10534,62 +10530,58 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>45.6</v>
+        <v>58.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>48</v>
+        <v>35.2</v>
       </c>
       <c r="R37" t="n">
-        <v>25.4</v>
+        <v>52.9</v>
       </c>
       <c r="S37" t="n">
-        <v>92.09999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="T37" t="n">
         <v>50</v>
       </c>
       <c r="U37" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10609,14 +10601,14 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="AJ37" t="inlineStr">
         <is>
           <t>0</t>
@@ -10624,12 +10616,12 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/30, 0 HR</t>
+          <t>Last 7 games: 1/5, 0 HR</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -10639,104 +10631,112 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>20.81</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>102.7713</t>
+          <t>104.7423</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.4531</t>
+          <t>0.3951</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.1873</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0.3635</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>66.92</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>38.28</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.1678</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.3882</t>
+          <t>0.4198</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.1581</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>29.25</t>
-        </is>
-      </c>
-      <c r="BG37" t="inlineStr"/>
-      <c r="BH37" t="inlineStr"/>
+          <t>28.61</t>
+        </is>
+      </c>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -12152,7 +12152,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -16344,7 +16344,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>80</v>
       </c>
       <c r="U58" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/14, 0 HR</t>
+          <t>Last 7 games: 2/15, 0 HR</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -17959,47 +17959,47 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-10T16:15:00Z</t>
+          <t>2026-09-10T20:10:00Z</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -18022,58 +18022,62 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>10.2</v>
+        <v>32.1</v>
       </c>
       <c r="Q64" t="n">
-        <v>35.2</v>
+        <v>49.4</v>
       </c>
       <c r="R64" t="n">
-        <v>52.9</v>
+        <v>25.4</v>
       </c>
       <c r="S64" t="n">
-        <v>86.40000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T64" t="n">
         <v>50</v>
       </c>
       <c r="U64" t="n">
-        <v>39.5</v>
+        <v>37.8</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC64" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18093,12 +18097,12 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -18108,12 +18112,12 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 5/20, 1 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.8% barrel, 24.2 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
@@ -18123,112 +18127,104 @@
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
+          <t>39.89</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>88.05</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>100.487</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>0.3543</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>0.139</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr">
+        <is>
+          <t>0.2701</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>74.34</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>43.58</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>37.58</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>27.1</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>0.1578</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>9.79</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>41.63</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>90.03</t>
+        </is>
+      </c>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>0.388</t>
+        </is>
+      </c>
+      <c r="BE64" t="inlineStr">
+        <is>
+          <t>0.1624</t>
+        </is>
+      </c>
+      <c r="BF64" t="inlineStr">
+        <is>
           <t>28.82</t>
         </is>
       </c>
-      <c r="AP64" t="inlineStr">
-        <is>
-          <t>85.9</t>
-        </is>
-      </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>96.2415</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>0.3632</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr">
-        <is>
-          <t>0.1008</t>
-        </is>
-      </c>
-      <c r="AT64" t="inlineStr">
-        <is>
-          <t>0.2969</t>
-        </is>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>68.87</t>
-        </is>
-      </c>
-      <c r="AV64" t="inlineStr">
-        <is>
-          <t>4.03</t>
-        </is>
-      </c>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>31.68</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>25.86</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>0.1182</t>
-        </is>
-      </c>
-      <c r="BA64" t="inlineStr">
-        <is>
-          <t>6.93</t>
-        </is>
-      </c>
-      <c r="BB64" t="inlineStr">
-        <is>
-          <t>33.59</t>
-        </is>
-      </c>
-      <c r="BC64" t="inlineStr">
-        <is>
-          <t>87.46</t>
-        </is>
-      </c>
-      <c r="BD64" t="inlineStr">
-        <is>
-          <t>0.4198</t>
-        </is>
-      </c>
-      <c r="BE64" t="inlineStr">
-        <is>
-          <t>0.153</t>
-        </is>
-      </c>
-      <c r="BF64" t="inlineStr">
-        <is>
-          <t>28.61</t>
-        </is>
-      </c>
-      <c r="BG64" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH64" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
+      <c r="BG64" t="inlineStr"/>
+      <c r="BH64" t="inlineStr"/>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -18239,47 +18235,47 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-10T20:10:00Z</t>
+          <t>2026-09-10T16:15:00Z</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -18288,7 +18284,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -18302,20 +18298,20 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>32.1</v>
+        <v>10.2</v>
       </c>
       <c r="Q65" t="n">
-        <v>49.4</v>
+        <v>35.2</v>
       </c>
       <c r="R65" t="n">
-        <v>25.4</v>
+        <v>52.9</v>
       </c>
       <c r="S65" t="n">
-        <v>40.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T65" t="n">
         <v>50</v>
@@ -18325,39 +18321,35 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18377,12 +18369,12 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -18392,12 +18384,12 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.8% barrel, 24.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 19.9 HR allowed</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
@@ -18407,104 +18399,112 @@
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>39.89</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>88.05</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>100.487</t>
+          <t>96.2415</t>
         </is>
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>0.3543</t>
+          <t>0.3632</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.1008</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>0.2701</t>
+          <t>0.2969</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>74.34</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>31.68</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>0.1578</t>
+          <t>0.1182</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="BD65" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.4198</t>
         </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
-          <t>0.1624</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>28.82</t>
-        </is>
-      </c>
-      <c r="BG65" t="inlineStr"/>
-      <c r="BH65" t="inlineStr"/>
+          <t>28.61</t>
+        </is>
+      </c>
+      <c r="BG65" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH65" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr"/>
@@ -18515,47 +18515,47 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>663611</t>
+          <t>804606</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nick Madrigal</t>
+          <t>Konnor Griffin</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-10T16:15:00Z</t>
+          <t>2026-09-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -18578,61 +18578,65 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>6.3</v>
+        <v>31.1</v>
       </c>
       <c r="Q66" t="n">
-        <v>40.2</v>
+        <v>14.1</v>
       </c>
       <c r="R66" t="n">
-        <v>52.9</v>
+        <v>27.6</v>
       </c>
       <c r="S66" t="n">
-        <v>76.2</v>
+        <v>88.7</v>
       </c>
       <c r="T66" t="n">
         <v>78</v>
       </c>
       <c r="U66" t="n">
-        <v>10.6</v>
+        <v>14.1</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr"/>
@@ -18649,12 +18653,12 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -18664,12 +18668,12 @@
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.4% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
@@ -18679,112 +18683,104 @@
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>95.8241</t>
+          <t>100.9613</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.389</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BD66" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.245</t>
         </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.074</t>
         </is>
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>23.92</t>
-        </is>
-      </c>
-      <c r="BG66" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH66" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="BG66" t="inlineStr"/>
+      <c r="BH66" t="inlineStr"/>
       <c r="BI66" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ66" t="inlineStr"/>
@@ -18795,47 +18791,47 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>804606</t>
+          <t>663611</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Konnor Griffin</t>
+          <t>Nick Madrigal</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-10T23:40:00Z</t>
+          <t>2026-09-10T16:15:00Z</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -18844,7 +18840,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -18858,65 +18854,61 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>31.1</v>
+        <v>6.3</v>
       </c>
       <c r="Q67" t="n">
-        <v>14.1</v>
+        <v>40.2</v>
       </c>
       <c r="R67" t="n">
-        <v>27.6</v>
+        <v>52.9</v>
       </c>
       <c r="S67" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T67" t="n">
         <v>78</v>
       </c>
       <c r="U67" t="n">
-        <v>14.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr"/>
@@ -18933,12 +18925,12 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -18948,12 +18940,12 @@
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.4% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
@@ -18963,104 +18955,112 @@
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>100.9613</t>
+          <t>95.8241</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.054</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>0.298</t>
         </is>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD67" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="BG67" t="inlineStr"/>
-      <c r="BH67" t="inlineStr"/>
+          <t>23.92</t>
+        </is>
+      </c>
+      <c r="BG67" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH67" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="BI67" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ67" t="inlineStr"/>
@@ -19899,52 +19899,52 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>671976</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-10T16:15:00Z</t>
+          <t>2026-09-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -19962,61 +19962,65 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>11.9</v>
+        <v>15.7</v>
       </c>
       <c r="Q71" t="n">
         <v>40.2</v>
       </c>
       <c r="R71" t="n">
-        <v>52.9</v>
+        <v>27.6</v>
       </c>
       <c r="S71" t="n">
-        <v>52.4</v>
+        <v>59.8</v>
       </c>
       <c r="T71" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U71" t="n">
-        <v>13.6</v>
+        <v>40.7</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr"/>
@@ -20033,12 +20037,12 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -20048,12 +20052,12 @@
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
@@ -20063,112 +20067,104 @@
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>35.87</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>87.36</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>98.9437</t>
+          <t>98.2253</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>0.3255</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>0.0909</t>
+          <t>0.1106</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>0.2728</t>
+          <t>0.2677</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>72.35</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.159</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>23.92</t>
-        </is>
-      </c>
-      <c r="BG71" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH71" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="BG71" t="inlineStr"/>
+      <c r="BH71" t="inlineStr"/>
       <c r="BI71" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ71" t="inlineStr"/>
@@ -20179,56 +20175,56 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>671976</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-10T23:40:00Z</t>
+          <t>2026-09-10T16:15:00Z</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -20242,65 +20238,61 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>15.7</v>
+        <v>11.9</v>
       </c>
       <c r="Q72" t="n">
         <v>40.2</v>
       </c>
       <c r="R72" t="n">
-        <v>27.6</v>
+        <v>52.9</v>
       </c>
       <c r="S72" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T72" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U72" t="n">
-        <v>40.7</v>
+        <v>12</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr"/>
@@ -20317,12 +20309,12 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -20332,12 +20324,12 @@
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 4/20, 0 HR</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
@@ -20347,104 +20339,112 @@
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>87.36</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>98.2253</t>
+          <t>98.9437</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3255</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>0.1106</t>
+          <t>0.0909</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>0.2677</t>
+          <t>0.2728</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>72.35</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>0.1309</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD72" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="BG72" t="inlineStr"/>
-      <c r="BH72" t="inlineStr"/>
+          <t>23.92</t>
+        </is>
+      </c>
+      <c r="BG72" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH72" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="BI72" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ72" t="inlineStr"/>
@@ -21056,7 +21056,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>50</v>
       </c>
       <c r="U75" t="n">
-        <v>13.6</v>
+        <v>12</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Last 7 games: 4/20, 0 HR</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -23000,7 +23000,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>50</v>
       </c>
       <c r="U82" t="n">
-        <v>17.3</v>
+        <v>15.3</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -23100,7 +23100,7 @@
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 4/18, 0 HR</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
@@ -24084,7 +24084,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -26070,7 +26070,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -26350,7 +26350,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -29154,7 +29154,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>40.7</v>
+        <v>39.2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -29254,7 +29254,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Last 7 games: 7/27, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -29661,52 +29661,52 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>703155</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Lazaro Montes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-10T16:15:00Z</t>
+          <t>2026-09-10T20:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -29724,61 +29724,65 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>46.2</v>
+        <v>65.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>40.2</v>
+        <v>48</v>
       </c>
       <c r="R15" t="n">
-        <v>52.9</v>
+        <v>25.4</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>59.8</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>28.2</v>
+        <v>58.1</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -29795,142 +29799,134 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/13, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>91.91</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>102.7587</t>
+          <t>99.6883</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4145</t>
+          <t>0.544</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1695</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>57.86</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1498</t>
+          <t>0.369</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.3882</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.1581</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>23.92</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
+          <t>29.25</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -29941,56 +29937,56 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>703155</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lazaro Montes</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-10T20:10:00Z</t>
+          <t>2026-09-10T16:15:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>55.3</v>
+        <v>55.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -30004,65 +30000,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>65.2</v>
+        <v>46.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>48</v>
+        <v>40.2</v>
       </c>
       <c r="R16" t="n">
-        <v>25.4</v>
+        <v>52.9</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>58.1</v>
+        <v>24.9</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -30079,134 +30071,142 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/14, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 10.9 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.91</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.6883</t>
+          <t>102.7587</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>0.4145</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.1695</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.323</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>57.86</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>0.1498</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3882</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1581</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>29.25</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>23.92</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -30818,7 +30818,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>54.6</v>
+        <v>54.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>59.3</v>
+        <v>57.2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -30918,7 +30918,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 11/28 over last 7 games</t>
+          <t>Contact streak: 11/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -31350,7 +31350,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-09-10.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-10.xlsx
@@ -1097,7 +1097,7 @@
         <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>81.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>75</v>
       </c>
       <c r="U6" t="n">
-        <v>54.9</v>
+        <v>52.5</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2415,24 +2415,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>686527</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Dominic Canzone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-09-10T20:10:00Z</t>
@@ -2445,17 +2445,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>57</v>
+        <v>56.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2482,22 +2482,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>49.2</v>
+        <v>54.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>49.4</v>
+        <v>48</v>
       </c>
       <c r="R8" t="n">
         <v>39.9</v>
       </c>
       <c r="S8" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>53.3</v>
+        <v>14.1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2549,27 +2549,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.8% barrel, 24.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2579,97 +2579,97 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.76</t>
+          <t>91.46</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.9862</t>
+          <t>102.5406</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>0.4952</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1936</t>
+          <t>0.222</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3592</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>72.53</t>
+          <t>73.94</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>43.18</t>
+          <t>40.04</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>0.2076</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.3882</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1624</t>
+          <t>0.1581</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -2695,24 +2695,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>686527</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-09-10T20:10:00Z</t>
@@ -2725,17 +2725,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>56.9</v>
+        <v>56.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2762,22 +2762,22 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>54.6</v>
+        <v>49.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>48</v>
+        <v>49.4</v>
       </c>
       <c r="R9" t="n">
         <v>39.9</v>
       </c>
       <c r="S9" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>14.1</v>
+        <v>50.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2829,27 +2829,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.8% barrel, 24.2 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2859,97 +2859,97 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.46</t>
+          <t>91.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.5406</t>
+          <t>101.9862</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4952</t>
+          <t>0.428</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>0.1936</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3592</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>72.53</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>25.27</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>43.18</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2076</t>
+          <t>0.217</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>90.03</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3882</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1581</t>
+          <t>0.1624</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/27, 0 HR</t>
+          <t>Last 7 games: 3/28, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/26, 0 HR</t>
+          <t>Last 7 games: 3/27, 0 HR</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
@@ -8657,7 +8657,7 @@
         <v>50</v>
       </c>
       <c r="U30" t="n">
-        <v>29.2</v>
+        <v>28.1</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>80</v>
       </c>
       <c r="U32" t="n">
-        <v>18</v>
+        <v>16.6</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -16543,7 +16543,7 @@
         <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>81.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -17350,7 +17350,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>75</v>
       </c>
       <c r="U6" t="n">
-        <v>54.9</v>
+        <v>52.5</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -17861,24 +17861,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>686527</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Dominic Canzone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-09-10T20:10:00Z</t>
@@ -17891,17 +17891,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -17910,7 +17910,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>57</v>
+        <v>56.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -17928,22 +17928,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>49.2</v>
+        <v>54.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>49.4</v>
+        <v>48</v>
       </c>
       <c r="R8" t="n">
         <v>39.9</v>
       </c>
       <c r="S8" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>53.3</v>
+        <v>14.1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -17995,27 +17995,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.8% barrel, 24.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -18025,97 +18025,97 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.76</t>
+          <t>91.46</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.9862</t>
+          <t>102.5406</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>0.4952</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1936</t>
+          <t>0.222</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3592</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>72.53</t>
+          <t>73.94</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>43.18</t>
+          <t>40.04</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>0.2076</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.3882</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1624</t>
+          <t>0.1581</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -18141,24 +18141,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>686527</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dominic Canzone</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-09-10T20:10:00Z</t>
@@ -18171,17 +18171,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -18190,7 +18190,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>56.9</v>
+        <v>56.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -18208,22 +18208,22 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>54.6</v>
+        <v>49.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>48</v>
+        <v>49.4</v>
       </c>
       <c r="R9" t="n">
         <v>39.9</v>
       </c>
       <c r="S9" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>14.1</v>
+        <v>50.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -18275,27 +18275,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 21.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.8% barrel, 24.2 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -18305,97 +18305,97 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.46</t>
+          <t>91.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.5406</t>
+          <t>101.9862</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4952</t>
+          <t>0.428</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>0.1936</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3592</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>72.53</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>25.27</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>43.18</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2076</t>
+          <t>0.217</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>90.03</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3882</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1581</t>
+          <t>0.1624</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -19410,7 +19410,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/27, 0 HR</t>
+          <t>Last 7 games: 3/28, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
